--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-80)_221026.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 10/NKSX_VNSH03-(SL-80)_221026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F51338-809F-451B-A3D5-5981E0D56372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109DD449-CF21-487C-BA97-856107891B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -360,9 +360,6 @@
     <t>80</t>
   </si>
   <si>
-    <t>Hà Nội, ngày 21 tháng 10 năm 2026</t>
-  </si>
-  <si>
     <t>VNET860879084177548</t>
   </si>
   <si>
@@ -601,6 +598,9 @@
   </si>
   <si>
     <t>VNET860879084180302</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày 22 tháng 10 năm 2026</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1673,7 @@
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
       <c r="H6" s="14" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1916,7 +1916,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1924,7 +1924,7 @@
         <v>29</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1932,7 +1932,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1940,7 +1940,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
         <v>32</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1956,7 +1956,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1964,7 +1964,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1972,7 +1972,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1980,7 +1980,7 @@
         <v>36</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1988,7 +1988,7 @@
         <v>37</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1996,7 +1996,7 @@
         <v>41</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2004,7 +2004,7 @@
         <v>42</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2012,7 +2012,7 @@
         <v>43</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2020,7 +2020,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2028,7 +2028,7 @@
         <v>45</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2036,7 +2036,7 @@
         <v>46</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2044,7 +2044,7 @@
         <v>47</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2052,7 +2052,7 @@
         <v>48</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2060,7 +2060,7 @@
         <v>49</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2068,7 +2068,7 @@
         <v>50</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>51</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2084,7 +2084,7 @@
         <v>52</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2092,7 +2092,7 @@
         <v>53</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2100,7 +2100,7 @@
         <v>54</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2108,7 +2108,7 @@
         <v>55</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2116,7 +2116,7 @@
         <v>56</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2124,7 +2124,7 @@
         <v>57</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2132,7 +2132,7 @@
         <v>58</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2140,7 +2140,7 @@
         <v>59</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2148,7 +2148,7 @@
         <v>61</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2156,7 +2156,7 @@
         <v>62</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2164,7 +2164,7 @@
         <v>63</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2172,7 +2172,7 @@
         <v>64</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2180,7 +2180,7 @@
         <v>65</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2188,7 +2188,7 @@
         <v>66</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2196,7 +2196,7 @@
         <v>67</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2204,7 +2204,7 @@
         <v>68</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2212,7 +2212,7 @@
         <v>69</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2220,7 +2220,7 @@
         <v>70</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2228,7 +2228,7 @@
         <v>71</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2236,7 +2236,7 @@
         <v>72</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2244,7 +2244,7 @@
         <v>73</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2252,7 +2252,7 @@
         <v>74</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2260,7 +2260,7 @@
         <v>75</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2268,7 +2268,7 @@
         <v>76</v>
       </c>
       <c r="B47" s="37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2276,7 +2276,7 @@
         <v>77</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2284,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="B49" s="37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2292,7 +2292,7 @@
         <v>78</v>
       </c>
       <c r="B50" s="37" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>79</v>
       </c>
       <c r="B51" s="37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2308,7 +2308,7 @@
         <v>80</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2316,7 +2316,7 @@
         <v>81</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2324,7 +2324,7 @@
         <v>82</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2332,7 +2332,7 @@
         <v>83</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
         <v>84</v>
       </c>
       <c r="B56" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2348,7 +2348,7 @@
         <v>85</v>
       </c>
       <c r="B57" s="37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2356,7 +2356,7 @@
         <v>86</v>
       </c>
       <c r="B58" s="37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2364,7 +2364,7 @@
         <v>87</v>
       </c>
       <c r="B59" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2372,7 +2372,7 @@
         <v>88</v>
       </c>
       <c r="B60" s="37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2380,7 +2380,7 @@
         <v>89</v>
       </c>
       <c r="B61" s="37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2388,7 +2388,7 @@
         <v>90</v>
       </c>
       <c r="B62" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2396,7 +2396,7 @@
         <v>91</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2404,7 +2404,7 @@
         <v>92</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2412,7 +2412,7 @@
         <v>93</v>
       </c>
       <c r="B65" s="37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2420,7 +2420,7 @@
         <v>94</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2428,7 +2428,7 @@
         <v>95</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2436,7 +2436,7 @@
         <v>96</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2444,7 +2444,7 @@
         <v>97</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2452,7 +2452,7 @@
         <v>98</v>
       </c>
       <c r="B70" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2460,7 +2460,7 @@
         <v>99</v>
       </c>
       <c r="B71" s="37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2468,7 +2468,7 @@
         <v>100</v>
       </c>
       <c r="B72" s="37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
         <v>101</v>
       </c>
       <c r="B73" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2484,7 +2484,7 @@
         <v>102</v>
       </c>
       <c r="B74" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2492,7 +2492,7 @@
         <v>103</v>
       </c>
       <c r="B75" s="37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2500,7 +2500,7 @@
         <v>104</v>
       </c>
       <c r="B76" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2508,7 +2508,7 @@
         <v>105</v>
       </c>
       <c r="B77" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2516,7 +2516,7 @@
         <v>106</v>
       </c>
       <c r="B78" s="37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2524,7 +2524,7 @@
         <v>107</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2532,7 +2532,7 @@
         <v>108</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2540,7 +2540,7 @@
         <v>109</v>
       </c>
       <c r="B81" s="37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2548,7 +2548,7 @@
         <v>110</v>
       </c>
       <c r="B82" s="37" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
